--- a/График_подготовки_Октоберфест.xlsx
+++ b/График_подготовки_Октоберфест.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Desktop\Новая папка\Заполнено_в работу\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Проекты\Королькова\Октоберфест\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B9EFB8-7ECC-4ACF-A275-409E9C4589B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E151F4-0A3C-482F-8B53-5A8E72C06E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
   <si>
     <t>График подготовки к фестивалю Октоберфест</t>
   </si>
@@ -150,9 +150,6 @@
   </si>
   <si>
     <t>Определить и утвердить локации для проведения фудовых и тематических мастер-классов и активностей, их количество и варианты</t>
-  </si>
-  <si>
-    <t>поиск диджея и заключение договора</t>
   </si>
   <si>
     <t>10.1.</t>
@@ -231,7 +228,19 @@
     <t>принято решение о необходимости утепления</t>
   </si>
   <si>
-    <t>изготовлено 25.09.26. Поставка ожидается 28.09.26</t>
+    <t>выполнено 28.09.26</t>
+  </si>
+  <si>
+    <t>Поиск диджея и заключение договора</t>
+  </si>
+  <si>
+    <t>реклама стартовала</t>
+  </si>
+  <si>
+    <t>7.1.</t>
+  </si>
+  <si>
+    <t>Проведение СМР по утеплению</t>
   </si>
 </sst>
 </file>
@@ -241,7 +250,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -285,6 +294,11 @@
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -366,7 +380,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -429,6 +443,9 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -438,8 +455,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -657,7 +674,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E78"/>
   </sheetPr>
-  <dimension ref="A2:E42"/>
+  <dimension ref="A2:E43"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="13" customWidth="1"/>
@@ -668,13 +685,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="11"/>
@@ -714,7 +731,7 @@
         <v>46276</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="33.5" customHeight="1">
@@ -731,7 +748,7 @@
         <v>46280</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20" customHeight="1">
@@ -748,7 +765,7 @@
         <v>46280</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="38" customHeight="1">
@@ -765,7 +782,7 @@
         <v>46280</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="33" customHeight="1">
@@ -782,7 +799,7 @@
         <v>46280</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="51.5" customHeight="1">
@@ -799,7 +816,7 @@
         <v>46280</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" customHeight="1">
@@ -813,228 +830,230 @@
         <v>46274</v>
       </c>
       <c r="D11" s="9">
+        <v>46274</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="34" customHeight="1">
+      <c r="A12" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="9">
+        <v>46290</v>
+      </c>
+      <c r="D12" s="9">
+        <v>46315</v>
+      </c>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" ht="34" customHeight="1">
+      <c r="A13" s="11">
+        <v>8</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46280</v>
+      </c>
+      <c r="D13" s="9">
         <v>46293</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="34" customHeight="1">
-      <c r="A12" s="11">
-        <v>8</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="9">
-        <v>46280</v>
-      </c>
-      <c r="D12" s="9">
-        <v>46293</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="45.5" customHeight="1">
-      <c r="A13" s="11">
+      <c r="E13" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="45.5" customHeight="1">
+      <c r="A14" s="11">
         <v>9</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C14" s="9">
         <v>46296</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D14" s="9">
         <v>46310</v>
       </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="20" customHeight="1">
-      <c r="A14" s="11">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="20" customHeight="1">
+      <c r="A15" s="11">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C15" s="21">
         <v>46274</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D15" s="21">
         <v>46290</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="20" customHeight="1">
-      <c r="A15" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="9">
-        <v>46274</v>
-      </c>
-      <c r="D15" s="9">
-        <v>46281</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
-      <c r="A16" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>27</v>
+      <c r="A16" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>26</v>
       </c>
       <c r="C16" s="9">
-        <v>46280</v>
+        <v>46274</v>
       </c>
       <c r="D16" s="9">
         <v>46281</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="20" customHeight="1">
-      <c r="A17" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="9">
+        <v>46280</v>
+      </c>
+      <c r="D17" s="9">
+        <v>46281</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="20" customHeight="1">
+      <c r="A18" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C18" s="9">
         <v>46276</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D18" s="9">
         <v>46289</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="20" customHeight="1">
-      <c r="A18" s="11">
+      <c r="E18" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="20" customHeight="1">
+      <c r="A19" s="11">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B19" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="20">
-        <f>C19</f>
+      <c r="C19" s="20">
+        <f>C20</f>
         <v>46277</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D19" s="20">
         <v>46320</v>
       </c>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" ht="20" customHeight="1">
-      <c r="A19" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="6">
-        <v>46277</v>
-      </c>
-      <c r="D19" s="6">
-        <v>46290</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5" ht="20" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="6">
-        <v>46293</v>
+        <v>46277</v>
       </c>
       <c r="D20" s="6">
-        <v>46296</v>
+        <v>46290</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="C21" s="6">
         <v>46293</v>
       </c>
       <c r="D21" s="6">
-        <v>46320</v>
-      </c>
-      <c r="E21" s="1"/>
+        <v>46296</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="20" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="20">
-        <v>46286</v>
-      </c>
-      <c r="D22" s="20">
-        <v>46318</v>
-      </c>
-      <c r="E22" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="6">
+        <v>46293</v>
+      </c>
+      <c r="D22" s="6">
+        <v>46320</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="20" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="20">
+        <v>46286</v>
+      </c>
+      <c r="D23" s="20">
+        <v>46318</v>
+      </c>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" ht="20" customHeight="1">
+      <c r="A24" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C24" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D24" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="1:5" ht="20" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="6">
-        <v>46286</v>
-      </c>
-      <c r="D24" s="6">
-        <v>46307</v>
       </c>
       <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:5" ht="20" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="C25" s="6">
         <v>46286</v>
@@ -1044,12 +1063,12 @@
       </c>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" ht="33.5" customHeight="1">
+    <row r="26" spans="1:5" ht="20" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="6">
         <v>46286</v>
@@ -1059,75 +1078,75 @@
       </c>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" ht="20" customHeight="1">
+    <row r="27" spans="1:5" ht="33.5" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B27" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>46286</v>
+      </c>
+      <c r="D27" s="6">
+        <v>46307</v>
+      </c>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" ht="20" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C28" s="6">
         <v>46296</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="1:5" ht="36" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:5" ht="36" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="6">
-        <v>46311</v>
+        <v>13</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:5" ht="36" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C30" s="6">
-        <v>46315</v>
-      </c>
-      <c r="D30" s="6">
-        <v>46317</v>
+        <v>46311</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="1:5" ht="36" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C31" s="6">
-        <v>46317</v>
+        <v>46315</v>
       </c>
       <c r="D31" s="6">
         <v>46317</v>
@@ -1136,28 +1155,28 @@
     </row>
     <row r="32" spans="1:5" ht="36" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C32" s="6">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D32" s="6">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:5" ht="36" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="C33" s="6">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="D33" s="6">
         <v>46318</v>
@@ -1166,10 +1185,10 @@
     </row>
     <row r="34" spans="1:5" ht="36" customHeight="1">
       <c r="A34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="19" t="s">
         <v>58</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>18</v>
       </c>
       <c r="C34" s="6">
         <v>46318</v>
@@ -1180,39 +1199,48 @@
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:5" ht="36" customHeight="1">
-      <c r="A35" s="13">
-        <v>13</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="16">
+      <c r="A35" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="6">
         <v>46318</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="6">
         <v>46318</v>
       </c>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" ht="36" customHeight="1">
       <c r="A36" s="13">
+        <v>13</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="16">
+        <v>46318</v>
+      </c>
+      <c r="D36" s="16">
+        <v>46318</v>
+      </c>
+      <c r="E36" s="5"/>
+    </row>
+    <row r="37" spans="1:5" ht="36" customHeight="1">
+      <c r="A37" s="13">
         <v>14</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B37" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C37" s="16">
         <v>46320</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D37" s="16">
         <v>46320</v>
       </c>
-      <c r="E36" s="5"/>
-    </row>
-    <row r="37" spans="1:5" ht="36" customHeight="1">
-      <c r="B37" s="18"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" ht="36" customHeight="1">
@@ -1222,10 +1250,9 @@
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" ht="36" customHeight="1">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" ht="36" customHeight="1">
@@ -1235,13 +1262,20 @@
       <c r="D40" s="6"/>
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:5">
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
+    <row r="41" spans="1:5" ht="36" customHeight="1">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5">
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
